--- a/excel_config/indir/技能表_战斗被动buff配置.xlsx
+++ b/excel_config/indir/技能表_战斗被动buff配置.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\godot\xiuxian\excel_config\indir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0AE320-3382-44CC-A6D6-161CC52EB439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4FD6E9-809F-406A-9A12-BBC1D0054CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="0" windowWidth="28650" windowHeight="14775" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="75" yWindow="390" windowWidth="28650" windowHeight="14775" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="z_zhandou_active" sheetId="1" r:id="rId1"/>
@@ -34,6 +34,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>唯一 ID；被其他表或存档引用时生效，同表内不能重复。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -47,6 +49,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>显示名；UI、日志、战斗单位名或道具名展示。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -60,6 +64,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>离散类型；按业务枚举或字符串分支生效。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -73,6 +79,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>物品/技能/功法阶位；用于门槛、颜色和数值缩放。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -86,6 +94,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>品质档；通常 1=下品、2=中品、3=上品、4=极品。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -99,6 +109,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>需求或归属境界；用于学习/使用门槛、展示分组或阶位推断。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -112,6 +124,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>标签数组/逗号列表；用于筛选、匹配、UI 标记。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -125,6 +139,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>战斗表现预设 ID；主动技能释放时由 VFX 索引找到 preset。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -138,6 +154,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>说明文本；详情面板、日志或剧情展示，不参与数值计算。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -151,6 +169,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>技能目标选择；可配 self/enemy/ally/all 等已支持值。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -164,6 +184,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>施法前摇秒数；主动技能开始释放到结算效果之间生效。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -177,6 +199,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>冷却秒数；技能释放后进入 CD。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -190,6 +214,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>消耗资源类型；与 cost_value 同时配置才生效。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -203,6 +229,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>消耗数值；大于 0 且 cost_resource 非空时加入技能消耗。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -216,6 +244,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>触发方式；主动技通常 cast，被动/常驻按运行时支持值。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -229,6 +259,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>效果配置数组；可配 damage/shield/heal_hp/restore_mana/attrschange/buff 等已登记效果。
 生效表：战斗主动技能表；玩家/怪物引用技能 ID 时生效。</t>
@@ -252,6 +284,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>唯一 ID；被其他表或存档引用时生效，同表内不能重复。
 生效表：战斗 Buff 表；技能 effects 配 buff 时生效。</t>
@@ -265,6 +299,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>显示名；UI、日志、战斗单位名或道具名展示。
 生效表：战斗 Buff 表；技能 effects 配 buff 时生效。</t>
@@ -278,6 +314,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>资源路径或图标 ID；UI 显示图标时生效。
 生效表：战斗 Buff 表；技能 effects 配 buff 时生效。</t>
@@ -291,6 +329,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>说明文本；详情面板、日志或剧情展示，不参与数值计算。
 生效表：战斗 Buff 表；技能 effects 配 buff 时生效。</t>
@@ -304,6 +344,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>离散类型；按业务枚举或字符串分支生效。
 生效表：战斗 Buff 表；技能 effects 配 buff 时生效。</t>
@@ -317,6 +359,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>持续时间秒数；Buff 或 VFX 步骤开始后计时。
 生效表：战斗 Buff 表；技能 effects 配 buff 时生效。</t>
@@ -330,6 +374,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>最大层数；Buff 叠加超过上限时截断。
 生效表：战斗 Buff 表；技能 effects 配 buff 时生效。</t>
@@ -343,6 +389,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>周期触发间隔秒；配置 tick_effects 时按此间隔结算。
 生效表：战斗 Buff 表；技能 effects 配 buff 时生效。</t>
@@ -356,6 +404,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>Buff 属性修正；Buff 存在期间修改对应战斗属性。
 生效表：战斗 Buff 表；技能 effects 配 buff 时生效。</t>
@@ -369,6 +419,8 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
           </rPr>
           <t>Buff 周期效果；每 ticktime 秒触发已登记战斗效果。
 生效表：战斗 Buff 表；技能 effects 配 buff 时生效。</t>
@@ -380,7 +432,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="205">
   <si>
     <t>ID</t>
   </si>
@@ -986,6 +1038,18 @@
   </si>
   <si>
     <t>damage:8</t>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1165,7 +1229,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1254,6 +1318,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2380,372 +2450,412 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="5" width="18.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="32.5" style="1" customWidth="1"/>
-    <col min="7" max="8" width="18.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="32.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="18.75" style="1" customWidth="1"/>
-    <col min="11" max="14" width="9" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="1"/>
+    <col min="1" max="6" width="18.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="32.5" style="1" customWidth="1"/>
+    <col min="8" max="9" width="18.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="32.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.75" style="1" customWidth="1"/>
+    <col min="12" max="15" width="9" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" customHeight="1">
+    <row r="1" spans="1:11" ht="18" customHeight="1">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="E1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="K1" s="14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
+    <row r="2" spans="1:11" ht="18" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="H2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="I2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
+    <row r="3" spans="1:11" ht="18" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>18</v>
+      <c r="C3" s="8" t="s">
+        <v>204</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="J3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
+    <row r="4" spans="1:11" ht="18" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>21</v>
       </c>
       <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
+      <c r="C4" s="8"/>
       <c r="D4" s="9"/>
-      <c r="E4" s="8"/>
+      <c r="E4" s="9"/>
       <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="9"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:10" ht="27" customHeight="1">
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" spans="1:11" ht="27" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>1</v>
       </c>
       <c r="D5" s="6">
         <v>1</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="6">
+        <v>1</v>
+      </c>
       <c r="F5" s="5"/>
-      <c r="G5" s="6">
+      <c r="G5" s="5"/>
+      <c r="H5" s="6">
         <v>0</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="27" customHeight="1">
+    <row r="6" spans="1:11" ht="27" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="6">
-        <v>4</v>
+      <c r="C6" s="5">
+        <v>1</v>
       </c>
       <c r="D6" s="6">
         <v>4</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="6">
+        <v>4</v>
+      </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="6">
+      <c r="G6" s="5"/>
+      <c r="H6" s="6">
         <v>5</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="27" customHeight="1">
+    <row r="7" spans="1:11" ht="27" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="6">
-        <v>3</v>
+      <c r="C7" s="5">
+        <v>1</v>
       </c>
       <c r="D7" s="6">
         <v>3</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="6">
+        <v>3</v>
+      </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="6">
+      <c r="G7" s="5"/>
+      <c r="H7" s="6">
         <v>8</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="I7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="J7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="K7" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="27" customHeight="1">
+    <row r="8" spans="1:11" ht="27" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="6">
-        <v>4</v>
+      <c r="C8" s="5">
+        <v>1</v>
       </c>
       <c r="D8" s="6">
         <v>4</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="6">
+        <v>4</v>
+      </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="6">
+      <c r="G8" s="5"/>
+      <c r="H8" s="6">
         <v>20</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="K8" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="27" customHeight="1">
+    <row r="9" spans="1:11" ht="27" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6">
         <v>7</v>
       </c>
-      <c r="D9" s="6">
+      <c r="E9" s="6">
         <v>4</v>
       </c>
-      <c r="E9" s="5"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="6">
+      <c r="G9" s="5"/>
+      <c r="H9" s="6">
         <v>6</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="I9" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="J9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="K9" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="27" customHeight="1">
+    <row r="10" spans="1:11" ht="27" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6">
         <v>8</v>
       </c>
-      <c r="D10" s="6">
+      <c r="E10" s="6">
         <v>4</v>
       </c>
-      <c r="E10" s="5"/>
       <c r="F10" s="5"/>
-      <c r="G10" s="6">
+      <c r="G10" s="5"/>
+      <c r="H10" s="6">
         <v>10</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="I10" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="J10" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="K10" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="27" customHeight="1">
+    <row r="11" spans="1:11" ht="27" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
         <v>9</v>
       </c>
-      <c r="D11" s="3">
+      <c r="E11" s="3">
         <v>4</v>
       </c>
-      <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="3">
+      <c r="G11" s="2"/>
+      <c r="H11" s="3">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="14.25" customHeight="1">
+    <row r="13" spans="1:11" ht="14.25" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="1">
-        <v>1</v>
+      <c r="C13" s="31">
+        <v>2</v>
       </c>
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="14.25" customHeight="1">
+    <row r="14" spans="1:11" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B14" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="1">
-        <v>1</v>
+      <c r="C14" s="31">
+        <v>2</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="14.25" customHeight="1">
+    <row r="15" spans="1:11" ht="14.25" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B15" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="1">
-        <v>1</v>
+      <c r="C15" s="31">
+        <v>2</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>24</v>
       </c>
     </row>
